--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{036F8686-A8FA-43AB-884D-2A7325CBB019}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379948B3-58CC-49E0-BAD3-6F13843FEB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11475" yWindow="-14910" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12210" yWindow="-13110" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -643,7 +643,7 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="F2">
         <v>20</v>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379948B3-58CC-49E0-BAD3-6F13843FEB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30703710-CFC0-4E2D-BA38-A7EB3E01DDF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12210" yWindow="-13110" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9060" yWindow="-14145" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -667,7 +667,7 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>10</v>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30703710-CFC0-4E2D-BA38-A7EB3E01DDF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5303BDEA-A600-43AE-B65A-791BF97600E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="-14145" windowWidth="15525" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -643,7 +643,7 @@
         <v>7</v>
       </c>
       <c r="E2">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="F2">
         <v>20</v>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5303BDEA-A600-43AE-B65A-791BF97600E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0085CB12-CE47-4823-BB86-5DD00A413FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="-14955" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -83,6 +83,18 @@
   </si>
   <si>
     <t>snow_enemy1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>urban_enemy1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>urban_enemy2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>actionID[]</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -106,15 +118,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -122,12 +140,29 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -153,9 +188,10 @@
       <sheetName val="Character"/>
       <sheetName val="Item"/>
       <sheetName val="Log"/>
+      <sheetName val="Action"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="A1" t="str">
@@ -201,130 +237,160 @@
           <cell r="A6">
             <v>1004</v>
           </cell>
+          <cell r="B6" t="str">
+            <v>都会敵1</v>
+          </cell>
         </row>
         <row r="7">
           <cell r="A7">
             <v>1005</v>
           </cell>
+          <cell r="B7" t="str">
+            <v>都会敵2</v>
+          </cell>
         </row>
         <row r="8">
           <cell r="A8">
             <v>1006</v>
           </cell>
+          <cell r="B8"/>
         </row>
         <row r="9">
           <cell r="A9">
             <v>1007</v>
           </cell>
+          <cell r="B9"/>
         </row>
         <row r="10">
           <cell r="A10">
             <v>1008</v>
           </cell>
+          <cell r="B10"/>
         </row>
         <row r="11">
           <cell r="A11">
             <v>1009</v>
           </cell>
+          <cell r="B11"/>
         </row>
         <row r="12">
           <cell r="A12">
             <v>1010</v>
           </cell>
+          <cell r="B12"/>
         </row>
         <row r="13">
           <cell r="A13">
             <v>1011</v>
           </cell>
+          <cell r="B13"/>
         </row>
         <row r="14">
           <cell r="A14">
             <v>1012</v>
           </cell>
+          <cell r="B14"/>
         </row>
         <row r="15">
           <cell r="A15">
             <v>1013</v>
           </cell>
+          <cell r="B15"/>
         </row>
         <row r="16">
           <cell r="A16">
             <v>1014</v>
           </cell>
+          <cell r="B16"/>
         </row>
         <row r="17">
           <cell r="A17">
             <v>1015</v>
           </cell>
+          <cell r="B17"/>
         </row>
         <row r="18">
           <cell r="A18">
             <v>1016</v>
           </cell>
+          <cell r="B18"/>
         </row>
         <row r="19">
           <cell r="A19">
             <v>1017</v>
           </cell>
+          <cell r="B19"/>
         </row>
         <row r="20">
           <cell r="A20">
             <v>1018</v>
           </cell>
+          <cell r="B20"/>
         </row>
         <row r="21">
           <cell r="A21">
             <v>1019</v>
           </cell>
+          <cell r="B21"/>
         </row>
         <row r="22">
           <cell r="A22">
             <v>1020</v>
           </cell>
+          <cell r="B22"/>
         </row>
         <row r="23">
           <cell r="A23">
             <v>1021</v>
           </cell>
+          <cell r="B23"/>
         </row>
         <row r="24">
           <cell r="A24">
             <v>1022</v>
           </cell>
+          <cell r="B24"/>
         </row>
         <row r="25">
           <cell r="A25">
             <v>1023</v>
           </cell>
+          <cell r="B25"/>
         </row>
         <row r="26">
           <cell r="A26">
             <v>1024</v>
           </cell>
+          <cell r="B26"/>
         </row>
         <row r="27">
           <cell r="A27">
             <v>1025</v>
           </cell>
+          <cell r="B27"/>
         </row>
         <row r="28">
           <cell r="A28">
             <v>1026</v>
           </cell>
+          <cell r="B28"/>
         </row>
         <row r="29">
           <cell r="A29">
             <v>1027</v>
           </cell>
+          <cell r="B29"/>
         </row>
         <row r="30">
           <cell r="A30">
             <v>1028</v>
           </cell>
+          <cell r="B30"/>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -593,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="3.375" bestFit="1" customWidth="1"/>
@@ -603,125 +669,258 @@
     <col min="5" max="5" width="4.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="8.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="10.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
+    <row r="2" spans="1:11">
+      <c r="A2" s="2">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>1000</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C2" s="2" t="str">
         <f>VLOOKUP(B2,[1]Character!$A:$B,2,FALSE)</f>
         <v>プレイヤー太郎</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>100</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>20</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>5</v>
       </c>
+      <c r="H2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="I2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J2" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
+    <row r="3" spans="1:11">
+      <c r="A3" s="2">
         <v>1</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>1001</v>
       </c>
-      <c r="C3" t="str">
+      <c r="C3" s="2" t="str">
         <f>VLOOKUP(B3,[1]Character!$A:$B,2,FALSE)</f>
         <v>エネミー1</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>20</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>10</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>1</v>
       </c>
+      <c r="H3" s="2">
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="J3" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
+    <row r="4" spans="1:11">
+      <c r="A4" s="2">
         <v>2</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>1002</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C4" s="2" t="str">
         <f>VLOOKUP(B4,[1]Character!$A:$B,2,FALSE)</f>
         <v>エネミー強</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>30</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>15</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>2</v>
       </c>
+      <c r="H4" s="2">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K4" s="2">
+        <v>-1</v>
+      </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
+    <row r="5" spans="1:11">
+      <c r="A5" s="2">
         <v>3</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>1003</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C5" s="2" t="str">
         <f>VLOOKUP(B5,[1]Character!$A:$B,2,FALSE)</f>
         <v>厄介な敵</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>21</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>20</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>3</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1004</v>
+      </c>
+      <c r="C6" s="2" t="str">
+        <f>VLOOKUP(B6,[1]Character!$A:$B,2,FALSE)</f>
+        <v>都会敵1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="2">
+        <v>40</v>
+      </c>
+      <c r="F6" s="2">
+        <v>25</v>
+      </c>
+      <c r="G6" s="2">
+        <v>4</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C7" s="2" t="str">
+        <f>VLOOKUP(B7,[1]Character!$A:$B,2,FALSE)</f>
+        <v>都会敵2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="2">
+        <v>51</v>
+      </c>
+      <c r="F7" s="2">
+        <v>30</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0085CB12-CE47-4823-BB86-5DD00A413FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1814CC6C-F0D0-4E59-A4FD-585213C9E39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="-14955" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="-14805" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -191,7 +191,7 @@
       <sheetName val="Action"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="A1" t="str">
@@ -253,144 +253,121 @@
           <cell r="A8">
             <v>1006</v>
           </cell>
-          <cell r="B8"/>
         </row>
         <row r="9">
           <cell r="A9">
             <v>1007</v>
           </cell>
-          <cell r="B9"/>
         </row>
         <row r="10">
           <cell r="A10">
             <v>1008</v>
           </cell>
-          <cell r="B10"/>
         </row>
         <row r="11">
           <cell r="A11">
             <v>1009</v>
           </cell>
-          <cell r="B11"/>
         </row>
         <row r="12">
           <cell r="A12">
             <v>1010</v>
           </cell>
-          <cell r="B12"/>
         </row>
         <row r="13">
           <cell r="A13">
             <v>1011</v>
           </cell>
-          <cell r="B13"/>
         </row>
         <row r="14">
           <cell r="A14">
             <v>1012</v>
           </cell>
-          <cell r="B14"/>
         </row>
         <row r="15">
           <cell r="A15">
             <v>1013</v>
           </cell>
-          <cell r="B15"/>
         </row>
         <row r="16">
           <cell r="A16">
             <v>1014</v>
           </cell>
-          <cell r="B16"/>
         </row>
         <row r="17">
           <cell r="A17">
             <v>1015</v>
           </cell>
-          <cell r="B17"/>
         </row>
         <row r="18">
           <cell r="A18">
             <v>1016</v>
           </cell>
-          <cell r="B18"/>
         </row>
         <row r="19">
           <cell r="A19">
             <v>1017</v>
           </cell>
-          <cell r="B19"/>
         </row>
         <row r="20">
           <cell r="A20">
             <v>1018</v>
           </cell>
-          <cell r="B20"/>
         </row>
         <row r="21">
           <cell r="A21">
             <v>1019</v>
           </cell>
-          <cell r="B21"/>
         </row>
         <row r="22">
           <cell r="A22">
             <v>1020</v>
           </cell>
-          <cell r="B22"/>
         </row>
         <row r="23">
           <cell r="A23">
             <v>1021</v>
           </cell>
-          <cell r="B23"/>
         </row>
         <row r="24">
           <cell r="A24">
             <v>1022</v>
           </cell>
-          <cell r="B24"/>
         </row>
         <row r="25">
           <cell r="A25">
             <v>1023</v>
           </cell>
-          <cell r="B25"/>
         </row>
         <row r="26">
           <cell r="A26">
             <v>1024</v>
           </cell>
-          <cell r="B26"/>
         </row>
         <row r="27">
           <cell r="A27">
             <v>1025</v>
           </cell>
-          <cell r="B27"/>
         </row>
         <row r="28">
           <cell r="A28">
             <v>1026</v>
           </cell>
-          <cell r="B28"/>
         </row>
         <row r="29">
           <cell r="A29">
             <v>1027</v>
           </cell>
-          <cell r="B29"/>
         </row>
         <row r="30">
           <cell r="A30">
             <v>1028</v>
           </cell>
-          <cell r="B30"/>
         </row>
       </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -803,10 +780,10 @@
         <v>2</v>
       </c>
       <c r="H4" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I4" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J4" s="2">
         <v>-1</v>
@@ -839,10 +816,10 @@
         <v>3</v>
       </c>
       <c r="H5" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I5" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J5" s="2">
         <v>-1</v>
@@ -875,10 +852,10 @@
         <v>4</v>
       </c>
       <c r="H6" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I6" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J6" s="2">
         <v>-1</v>
@@ -911,10 +888,10 @@
         <v>5</v>
       </c>
       <c r="H7" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I7" s="2">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="J7" s="2">
         <v>-1</v>

--- a/Assets/Resources/MasterData/CharacterData.xlsx
+++ b/Assets/Resources/MasterData/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ゲーム開発Ⅰ\UnityProject\2DRoguelike\Assets\Resources\MasterData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1814CC6C-F0D0-4E59-A4FD-585213C9E39C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75D19087-B07F-4729-A556-B142181D46C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="-14805" windowWidth="21915" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="-12645" windowWidth="16995" windowHeight="12015" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CharacterData" sheetId="1" r:id="rId1"/>
@@ -189,9 +189,10 @@
       <sheetName val="Item"/>
       <sheetName val="Log"/>
       <sheetName val="Action"/>
+      <sheetName val="Trap"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="1">
           <cell r="A1" t="str">
@@ -253,121 +254,151 @@
           <cell r="A8">
             <v>1006</v>
           </cell>
+          <cell r="B8"/>
         </row>
         <row r="9">
           <cell r="A9">
             <v>1007</v>
           </cell>
+          <cell r="B9"/>
         </row>
         <row r="10">
           <cell r="A10">
             <v>1008</v>
           </cell>
+          <cell r="B10"/>
         </row>
         <row r="11">
           <cell r="A11">
             <v>1009</v>
           </cell>
+          <cell r="B11"/>
         </row>
         <row r="12">
           <cell r="A12">
             <v>1010</v>
           </cell>
+          <cell r="B12"/>
         </row>
         <row r="13">
           <cell r="A13">
             <v>1011</v>
           </cell>
+          <cell r="B13"/>
         </row>
         <row r="14">
           <cell r="A14">
             <v>1012</v>
           </cell>
+          <cell r="B14"/>
         </row>
         <row r="15">
           <cell r="A15">
             <v>1013</v>
           </cell>
+          <cell r="B15"/>
         </row>
         <row r="16">
           <cell r="A16">
             <v>1014</v>
           </cell>
+          <cell r="B16"/>
         </row>
         <row r="17">
           <cell r="A17">
             <v>1015</v>
           </cell>
+          <cell r="B17"/>
         </row>
         <row r="18">
           <cell r="A18">
             <v>1016</v>
           </cell>
+          <cell r="B18"/>
         </row>
         <row r="19">
           <cell r="A19">
             <v>1017</v>
           </cell>
+          <cell r="B19"/>
         </row>
         <row r="20">
           <cell r="A20">
             <v>1018</v>
           </cell>
+          <cell r="B20"/>
         </row>
         <row r="21">
           <cell r="A21">
             <v>1019</v>
           </cell>
+          <cell r="B21"/>
         </row>
         <row r="22">
           <cell r="A22">
             <v>1020</v>
           </cell>
+          <cell r="B22"/>
         </row>
         <row r="23">
           <cell r="A23">
             <v>1021</v>
           </cell>
+          <cell r="B23"/>
         </row>
         <row r="24">
           <cell r="A24">
             <v>1022</v>
           </cell>
+          <cell r="B24"/>
         </row>
         <row r="25">
           <cell r="A25">
             <v>1023</v>
           </cell>
+          <cell r="B25"/>
         </row>
         <row r="26">
           <cell r="A26">
             <v>1024</v>
           </cell>
+          <cell r="B26"/>
         </row>
         <row r="27">
           <cell r="A27">
             <v>1025</v>
           </cell>
+          <cell r="B27"/>
         </row>
         <row r="28">
           <cell r="A28">
             <v>1026</v>
           </cell>
+          <cell r="B28"/>
         </row>
         <row r="29">
           <cell r="A29">
             <v>1027</v>
           </cell>
+          <cell r="B29"/>
         </row>
         <row r="30">
           <cell r="A30">
             <v>1028</v>
           </cell>
+          <cell r="B30"/>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>ID</v>
+          </cell>
+        </row>
+      </sheetData>
     </sheetDataSet>
   </externalBook>
 </externalLink>
